--- a/Protokol_proverki_znanii_OT.xlsx
+++ b/Protokol_proverki_znanii_OT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Denis\Desktop\Минтруд\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Denis\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D7D269-35A2-4337-AF31-8E1C90162B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C5140-E982-4905-B509-58580379D775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21333" windowHeight="12613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="2393" windowWidth="19845" windowHeight="10432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -225,28 +225,25 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,59 +548,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA2765B-1DA4-40E8-84B5-A0913C91733D}">
   <dimension ref="A2:H40"/>
-  <sheetFormatPr defaultRowHeight="13.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.52734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1171875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.52734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.05859375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.87890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.29296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1171875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.9375" style="1"/>
+    <col min="1" max="1" width="3.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.53125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.06640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.86328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1328125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.9296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="5" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="14" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="5" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="2:8" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="2:8" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -614,139 +611,139 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-    </row>
-    <row r="9" spans="2:8" ht="29" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="17" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="2:8" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="2:8" s="4" customFormat="1" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="18" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="2:8" s="4" customFormat="1" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B11" s="19" t="s">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="19"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B12" s="16" t="s">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="2:8" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:8" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" spans="2:8" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="16" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" spans="2:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="16"/>
+      <c r="C14" s="13"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="20">
+    <row r="20" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="19">
         <v>1</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-    </row>
-    <row r="21" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="20">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="19">
         <v>2</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-    </row>
-    <row r="22" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="20">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="19">
         <v>3</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="20">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+    </row>
+    <row r="23" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="19">
         <v>4</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-    </row>
-    <row r="24" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="20">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+    </row>
+    <row r="24" spans="1:8" s="9" customFormat="1" ht="31.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="19">
         <v>5</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-    </row>
-    <row r="27" spans="1:8" ht="90.7" x14ac:dyDescent="0.4">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="27" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
@@ -772,7 +769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" ht="55.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -784,65 +781,57 @@
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B30" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:8" ht="11.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" ht="11.35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B32" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D34" s="8"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="2:4" ht="7.35" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:4" ht="7.35" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="2:4" ht="9.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:4" ht="7.35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:4" ht="7.35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="2:4" ht="9.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="5" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B24:H24"/>
+  <mergeCells count="7">
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>
